--- a/heartpigeon/heartpigeon_DB.xlsx
+++ b/heartpigeon/heartpigeon_DB.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-P10\Desktop\cording\kafella92.github.io\heartpigeon\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16EC55F-E1C1-44A0-8830-3D22D5E85DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="2280" windowWidth="16245" windowHeight="11385" xr2:uid="{A2D55BA9-C27C-442C-9969-636D77FCC563}"/>
+    <workbookView xWindow="9516" yWindow="2280" windowWidth="16248" windowHeight="11388"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
   <si>
     <t>user 선물하는사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,13 +155,109 @@
   </si>
   <si>
     <t>12: 1500000~2999999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recipient 선물받는사람</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rno</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rrelative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rgen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhobby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rlike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rplace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 가족</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 친척</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 친구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 생일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 기념일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 주류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 궐련</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 화장품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 의상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 독서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인도어 &lt;-&gt; 아웃도어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가까운 &lt;-&gt; 격식있는</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heart = money :)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. nonCheck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 인테리어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 홈시어터</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -185,20 +275,59 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3300"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -207,8 +336,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -217,6 +364,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF3300"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -271,7 +423,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -323,7 +475,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -517,145 +669,356 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D56E5051-B2FE-453A-B353-2B1307456D84}">
-  <dimension ref="B2:F15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:N15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8984375" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D4" t="s">
+      <c r="H3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D5" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D7" t="s">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D8" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D9" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D10" t="s">
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F11" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D12" t="s">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F12" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D13" t="s">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F13" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D14" t="s">
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="D15" t="s">
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F15" t="s">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/heartpigeon/heartpigeon_DB.xlsx
+++ b/heartpigeon/heartpigeon_DB.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
   <si>
     <t>user 선물하는사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -251,6 +251,30 @@
   </si>
   <si>
     <t>2. 홈시어터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>친근한 &lt;-&gt; 격식 필요한</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 스승의날</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. 상견례</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 거래처미팅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. 결혼식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presentList</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -677,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:N15"/>
+  <dimension ref="B2:P15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
@@ -687,9 +711,11 @@
     <col min="8" max="8" width="20.69921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.19921875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -705,8 +731,14 @@
       <c r="K2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -744,7 +776,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -776,7 +808,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -808,7 +840,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -836,9 +868,11 @@
       <c r="M6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="N6" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -858,9 +892,11 @@
       <c r="M7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="N7" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -878,9 +914,11 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="N8" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -898,9 +936,11 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="N9" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -920,7 +960,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -940,7 +980,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -960,7 +1000,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -980,7 +1020,7 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1000,7 +1040,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">

--- a/heartpigeon/heartpigeon_DB.xlsx
+++ b/heartpigeon/heartpigeon_DB.xlsx
@@ -1,34 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-P10\Desktop\cording\kafella92.github.io\heartpigeon\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF74251E-88B0-4C44-B28D-980145159476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9516" yWindow="2280" windowWidth="16248" windowHeight="11388"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DB" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
   <si>
     <t>user 선물하는사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -222,10 +219,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4. 의상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 독서</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -274,14 +267,66 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>presentList</t>
+    <t>gift 선물 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gno</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gclass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gtype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 의류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gprice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gbrand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 실용형(의류, 위생용품,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대분류(실용, 취향, 감성, 경험)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gcategory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중분류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종류(제품, 서비스)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브랜드(제품, 장소,</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -299,7 +344,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -327,6 +372,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -360,7 +417,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -380,6 +437,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,52 +756,70 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:P15"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:U15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8984375" customWidth="1"/>
+    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.8984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N2" t="s">
-        <v>56</v>
-      </c>
-      <c r="P2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" t="s">
+        <v>71</v>
+      </c>
+      <c r="T2" t="s">
+        <v>73</v>
+      </c>
+      <c r="U2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -775,8 +856,26 @@
       <c r="N3" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -796,7 +895,7 @@
         <v>8</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>6</v>
@@ -807,8 +906,16 @@
       <c r="N4" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4" s="8"/>
+      <c r="S4" s="8"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -828,7 +935,7 @@
         <v>9</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>7</v>
@@ -839,15 +946,21 @@
       <c r="N5" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>22</v>
@@ -860,19 +973,25 @@
         <v>10</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>47</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -890,13 +1009,21 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8">
+        <v>4</v>
+      </c>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -915,10 +1042,16 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -937,10 +1070,16 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -959,8 +1098,14 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -979,8 +1124,14 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -999,8 +1150,14 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -1019,8 +1176,14 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1039,8 +1202,14 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
@@ -1059,6 +1228,12 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/heartpigeon/heartpigeon_DB.xlsx
+++ b/heartpigeon/heartpigeon_DB.xlsx
@@ -1,19 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-P10\Desktop\cording\kafella92.github.io\heartpigeon\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF74251E-88B0-4C44-B28D-980145159476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet name="DB" sheetId="1" r:id="rId1"/>
+    <sheet name="normalization" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
@@ -326,7 +322,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -756,32 +752,32 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:U15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8984375" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.8984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -819,7 +815,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -875,7 +871,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -915,7 +911,7 @@
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -953,7 +949,7 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -991,7 +987,7 @@
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -1023,7 +1019,7 @@
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -1051,7 +1047,7 @@
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -1079,7 +1075,7 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -1105,7 +1101,7 @@
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -1131,7 +1127,7 @@
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -1157,7 +1153,7 @@
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -1183,7 +1179,7 @@
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1209,7 +1205,7 @@
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
@@ -1240,4 +1236,24 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/heartpigeon/heartpigeon_DB.xlsx
+++ b/heartpigeon/heartpigeon_DB.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-P10\Desktop\cording\kafella92.github.io\heartpigeon\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8914BA-5B03-46E1-93BC-48A840C8CC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23256" windowHeight="13176"/>
+    <workbookView xWindow="11700" yWindow="1485" windowWidth="16245" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB" sheetId="1" r:id="rId1"/>
@@ -21,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
   <si>
     <t>user 선물하는사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -291,10 +297,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1. 실용형(의류, 위생용품,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>대분류(실용, 취향, 감성, 경험)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -316,13 +318,53 @@
   </si>
   <si>
     <t>브랜드(제품, 장소,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1: 실용형(의류, 위생, 건강, 전자기기)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2: 취향형(위스키, 디저트, 원두, 시가, 책)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3: 감성형(편지, 커플템, 꽃, DIY키트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4: 경험형(티켓, 원데이클래스, 숙박권)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10: 의류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11: 위생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12: 건강보충제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13: 전자기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. 스승</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. none</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -752,32 +794,33 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:U15"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:U23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8984375" customWidth="1"/>
+    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.8984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="26.8984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,22 +843,22 @@
         <v>60</v>
       </c>
       <c r="Q2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S2" t="s">
         <v>70</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U2" t="s">
         <v>71</v>
       </c>
-      <c r="T2" t="s">
-        <v>73</v>
-      </c>
-      <c r="U2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -856,7 +899,7 @@
         <v>61</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R3" s="7" t="s">
         <v>62</v>
@@ -871,7 +914,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -904,14 +947,16 @@
       </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="R4" s="8"/>
+        <v>73</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
       <c r="U4" s="8"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -943,13 +988,17 @@
         <v>44</v>
       </c>
       <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
+      <c r="Q5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>78</v>
+      </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -981,13 +1030,17 @@
         <v>56</v>
       </c>
       <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
+      <c r="Q6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="S6" s="8"/>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -1011,15 +1064,17 @@
         <v>58</v>
       </c>
       <c r="P7" s="8"/>
-      <c r="Q7" s="8">
-        <v>4</v>
-      </c>
-      <c r="R7" s="8"/>
+      <c r="Q7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>80</v>
+      </c>
       <c r="S7" s="8"/>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -1036,7 +1091,9 @@
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="N8" s="3" t="s">
         <v>57</v>
       </c>
@@ -1047,7 +1104,7 @@
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -1075,7 +1132,7 @@
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
     </row>
-    <row r="10" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -1086,7 +1143,9 @@
         <v>26</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="J10" s="3" t="s">
         <v>14</v>
       </c>
@@ -1101,7 +1160,7 @@
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
     </row>
-    <row r="11" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -1127,7 +1186,7 @@
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
     </row>
-    <row r="12" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -1153,7 +1212,7 @@
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
     </row>
-    <row r="13" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -1179,7 +1238,7 @@
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
     </row>
-    <row r="14" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1205,7 +1264,7 @@
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
     </row>
-    <row r="15" spans="2:21" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
@@ -1231,6 +1290,70 @@
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
     </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+    </row>
+    <row r="17" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+    </row>
+    <row r="18" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+    </row>
+    <row r="19" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+    </row>
+    <row r="20" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+    </row>
+    <row r="21" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+    </row>
+    <row r="22" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+    </row>
+    <row r="23" spans="16:21" x14ac:dyDescent="0.3">
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1239,9 +1362,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1249,9 +1372,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/heartpigeon/heartpigeon_DB.xlsx
+++ b/heartpigeon/heartpigeon_DB.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-P10\Desktop\cording\kafella92.github.io\heartpigeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8914BA-5B03-46E1-93BC-48A840C8CC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BF4180-3804-4068-9E02-418AAF7DA23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11700" yWindow="1485" windowWidth="16245" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10305" yWindow="-315" windowWidth="16245" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DB" sheetId="1" r:id="rId1"/>
-    <sheet name="normalization" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="DB(user_gift)" sheetId="1" r:id="rId1"/>
+    <sheet name="DB(mindtest)" sheetId="4" r:id="rId2"/>
+    <sheet name="normalization(mindtest)" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
   <si>
     <t>user 선물하는사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -165,10 +166,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rrelative</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -185,22 +182,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rplace</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 가족</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2. 친척</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. 친구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 생일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -229,10 +214,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>가까운 &lt;-&gt; 격식있는</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>heart = money :)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -249,10 +230,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>친근한 &lt;-&gt; 격식 필요한</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3. 스승의날</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -281,10 +258,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>gtype</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4. 의류</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -309,10 +282,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>종류(제품, 서비스)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>가격</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -353,11 +322,103 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7. 스승</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5. none</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 : nonCheck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cno</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crelative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cplace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low 가깝다 high 멀다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 스승</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. 비즈니스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 친구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 친척</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. 초면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Question 질문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qtext</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qorder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qno (PK)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Q1 다양한 선물을 준비한 당신, 선물받을 그 사람이 가장 먼저 할 말은?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Q4 근사한 레스토랑에 함께 간 그 사람은 어떤 술을 시킬까?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Answer 답변</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ano</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>printRule 출력 조합 규칙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Context 맥락</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uno(FK)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rno(FK)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pno</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>page</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -382,7 +443,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -425,8 +486,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -449,13 +546,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -481,6 +609,48 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -548,7 +718,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -600,7 +770,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -802,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:U23"/>
+  <dimension ref="B2:AG40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
@@ -810,55 +980,62 @@
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N2" t="s">
-        <v>55</v>
-      </c>
-      <c r="P2" s="7" t="s">
+      <c r="J2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" s="10"/>
+      <c r="N2" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" t="s">
-        <v>67</v>
-      </c>
-      <c r="R2" t="s">
-        <v>69</v>
-      </c>
-      <c r="S2" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>62</v>
+      </c>
+      <c r="W2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z2" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -881,40 +1058,59 @@
         <v>34</v>
       </c>
       <c r="J3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="7" t="s">
+      <c r="M3" s="9"/>
+      <c r="N3" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="U3" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V3" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z3" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -928,35 +1124,46 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="S4" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="M4" s="9"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-    </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="U4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="22"/>
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="22"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="22"/>
+      <c r="AG4" s="22"/>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -970,77 +1177,99 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="S5" s="8"/>
+        <v>42</v>
+      </c>
+      <c r="M5" s="9"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="R5" s="14" t="s">
+        <v>40</v>
+      </c>
       <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-    </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="U5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="22"/>
+      <c r="AC5" s="22"/>
+      <c r="AD5" s="22"/>
+      <c r="AE5" s="22"/>
+      <c r="AF5" s="22"/>
+      <c r="AG5" s="22"/>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="S6" s="8"/>
+        <v>48</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="9"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="U6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
+      <c r="AE6" s="22"/>
+      <c r="AF6" s="22"/>
+      <c r="AG6" s="22"/>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -1051,30 +1280,43 @@
         <v>23</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="S7" s="8"/>
+      <c r="L7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="9"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="R7" s="14" t="s">
+        <v>52</v>
+      </c>
       <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="U7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
+      <c r="AE7" s="22"/>
+      <c r="AF7" s="22"/>
+      <c r="AG7" s="22"/>
+    </row>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -1085,26 +1327,39 @@
         <v>24</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
+      <c r="L8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" s="9"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
+      <c r="AE8" s="22"/>
+      <c r="AF8" s="22"/>
+      <c r="AG8" s="22"/>
+    </row>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -1115,24 +1370,37 @@
         <v>25</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="R9" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
+      <c r="AE9" s="22"/>
+      <c r="AF9" s="22"/>
+      <c r="AG9" s="22"/>
+    </row>
+    <row r="10" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -1144,23 +1412,32 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J10" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="14"/>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
+      <c r="AE10" s="22"/>
+      <c r="AF10" s="22"/>
+      <c r="AG10" s="22"/>
+    </row>
+    <row r="11" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -1171,22 +1448,33 @@
         <v>27</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="14"/>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="22"/>
+      <c r="AF11" s="22"/>
+      <c r="AG11" s="22"/>
+    </row>
+    <row r="12" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -1197,22 +1485,33 @@
         <v>28</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
+      <c r="AE12" s="22"/>
+      <c r="AF12" s="22"/>
+      <c r="AG12" s="22"/>
+    </row>
+    <row r="13" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -1223,22 +1522,33 @@
         <v>29</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22"/>
+    </row>
+    <row r="14" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1249,22 +1559,33 @@
         <v>30</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="22"/>
+      <c r="AF14" s="22"/>
+      <c r="AG14" s="22"/>
+    </row>
+    <row r="15" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
@@ -1275,84 +1596,365 @@
         <v>31</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
+      <c r="AE15" s="22"/>
+      <c r="AF15" s="22"/>
+      <c r="AG15" s="22"/>
+    </row>
+    <row r="16" spans="2:33" x14ac:dyDescent="0.3">
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
-    </row>
-    <row r="17" spans="16:21" x14ac:dyDescent="0.3">
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="22"/>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
+    </row>
+    <row r="17" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
-    </row>
-    <row r="18" spans="16:21" x14ac:dyDescent="0.3">
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
+      <c r="AE17" s="22"/>
+      <c r="AF17" s="22"/>
+      <c r="AG17" s="22"/>
+    </row>
+    <row r="18" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
-    </row>
-    <row r="19" spans="16:21" x14ac:dyDescent="0.3">
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
+      <c r="AE18" s="22"/>
+      <c r="AF18" s="22"/>
+      <c r="AG18" s="22"/>
+    </row>
+    <row r="19" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
-    </row>
-    <row r="20" spans="16:21" x14ac:dyDescent="0.3">
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="22"/>
+      <c r="AF19" s="22"/>
+      <c r="AG19" s="22"/>
+    </row>
+    <row r="20" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
-    </row>
-    <row r="21" spans="16:21" x14ac:dyDescent="0.3">
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
+      <c r="AE20" s="22"/>
+      <c r="AF20" s="22"/>
+      <c r="AG20" s="22"/>
+    </row>
+    <row r="21" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
-    </row>
-    <row r="22" spans="16:21" x14ac:dyDescent="0.3">
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="8"/>
+      <c r="X21" s="8"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="22"/>
+      <c r="AE21" s="22"/>
+      <c r="AF21" s="22"/>
+      <c r="AG21" s="22"/>
+    </row>
+    <row r="22" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
-    </row>
-    <row r="23" spans="16:21" x14ac:dyDescent="0.3">
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
+      <c r="AE22" s="22"/>
+      <c r="AF22" s="22"/>
+      <c r="AG22" s="22"/>
+    </row>
+    <row r="23" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="8"/>
+      <c r="X23" s="8"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
+      <c r="AE23" s="22"/>
+      <c r="AF23" s="22"/>
+      <c r="AG23" s="22"/>
+    </row>
+    <row r="24" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+    </row>
+    <row r="25" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+    </row>
+    <row r="26" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+    </row>
+    <row r="27" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+    </row>
+    <row r="28" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+    </row>
+    <row r="29" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+    </row>
+    <row r="30" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+    </row>
+    <row r="31" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+    </row>
+    <row r="32" spans="9:33" x14ac:dyDescent="0.3">
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+    </row>
+    <row r="33" spans="9:17" x14ac:dyDescent="0.3">
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+    </row>
+    <row r="34" spans="9:17" x14ac:dyDescent="0.3">
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+    </row>
+    <row r="35" spans="9:17" x14ac:dyDescent="0.3">
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+    </row>
+    <row r="36" spans="9:17" x14ac:dyDescent="0.3">
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+    </row>
+    <row r="37" spans="9:17" x14ac:dyDescent="0.3">
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+    </row>
+    <row r="38" spans="9:17" x14ac:dyDescent="0.3">
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+    </row>
+    <row r="39" spans="9:17" x14ac:dyDescent="0.3">
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+    </row>
+    <row r="40" spans="9:17" x14ac:dyDescent="0.3">
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1362,6 +1964,108 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB14CF65-C935-4081-8098-F1DF22D1ECCF}">
+  <dimension ref="B2:G14"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="63" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1371,7 +2075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
